--- a/XBRL-template-MPERS/Group/09-SOCIE.xlsx
+++ b/XBRL-template-MPERS/Group/09-SOCIE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOCIE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SOCIE" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,12 +428,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,9 +455,81 @@
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Issued capital</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Treasury shares</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Capital reserve</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Foreign currency translation reserve</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Revaluation surplus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Other non-distributable reserves</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sub-total of non-distributable reserves</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Other distributable reserves</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners of parent</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Equity, others components</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
@@ -475,6 +560,22 @@
           <t>Equity at beginning of period</t>
         </is>
       </c>
+      <c r="I6">
+        <f>E6+F6+G6+H6</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>I6+J6</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>B6+C6+D6+K6</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>L6+M6+N6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -482,6 +583,22 @@
           <t>Impact of changes in accounting policies</t>
         </is>
       </c>
+      <c r="I7">
+        <f>E7+F7+G7+H7</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>I7+J7</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>B7+C7+D7+K7</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>L7+M7+N7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -489,6 +606,22 @@
           <t>Equity at beginning of period, restated</t>
         </is>
       </c>
+      <c r="I8">
+        <f>E8+F8+G8+H8</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>I8+J8</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>B8+C8+D8+K8</f>
+        <v/>
+      </c>
+      <c r="O8">
+        <f>L8+M8+N8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -510,6 +643,22 @@
           <t>Profit (loss)</t>
         </is>
       </c>
+      <c r="I11">
+        <f>E11+F11+G11+H11</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>I11+J11</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>B11+C11+D11+K11</f>
+        <v/>
+      </c>
+      <c r="O11">
+        <f>L11+M11+N11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -517,6 +666,22 @@
           <t>Total other comprehensive income</t>
         </is>
       </c>
+      <c r="I12">
+        <f>E12+F12+G12+H12</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>I12+J12</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>B12+C12+D12+K12</f>
+        <v/>
+      </c>
+      <c r="O12">
+        <f>L12+M12+N12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -528,6 +693,58 @@
         <f>1*B11+1*B12</f>
         <v/>
       </c>
+      <c r="C13">
+        <f>1*C11+1*C12</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>1*D11+1*D12</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>1*E11+1*E12</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>1*F11+1*F12</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>1*G11+1*G12</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>1*H11+1*H12</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>E13+F13+G13+H13</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>1*J11+1*J12</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>I13+J13</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>B13+C13+D13+K13</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>1*M11+1*M12</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>1*N11+1*N12</f>
+        <v/>
+      </c>
+      <c r="O13">
+        <f>L13+M13+N13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -542,6 +759,22 @@
           <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
+      <c r="I15">
+        <f>E15+F15+G15+H15</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>I15+J15</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>B15+C15+D15+K15</f>
+        <v/>
+      </c>
+      <c r="O15">
+        <f>L15+M15+N15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -549,6 +782,22 @@
           <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
+      <c r="I16">
+        <f>E16+F16+G16+H16</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>I16+J16</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>B16+C16+D16+K16</f>
+        <v/>
+      </c>
+      <c r="O16">
+        <f>L16+M16+N16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -556,6 +805,22 @@
           <t>Dividends paid</t>
         </is>
       </c>
+      <c r="I17">
+        <f>E17+F17+G17+H17</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>I17+J17</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>B17+C17+D17+K17</f>
+        <v/>
+      </c>
+      <c r="O17">
+        <f>L17+M17+N17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -563,6 +828,22 @@
           <t>Issuance of shares</t>
         </is>
       </c>
+      <c r="I18">
+        <f>E18+F18+G18+H18</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>I18+J18</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>B18+C18+D18+K18</f>
+        <v/>
+      </c>
+      <c r="O18">
+        <f>L18+M18+N18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -570,6 +851,22 @@
           <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
+      <c r="I19">
+        <f>E19+F19+G19+H19</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>I19+J19</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>B19+C19+D19+K19</f>
+        <v/>
+      </c>
+      <c r="O19">
+        <f>L19+M19+N19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -577,6 +874,22 @@
           <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
+      <c r="I20">
+        <f>E20+F20+G20+H20</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>I20+J20</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>B20+C20+D20+K20</f>
+        <v/>
+      </c>
+      <c r="O20">
+        <f>L20+M20+N20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -584,6 +897,22 @@
           <t>Treasury shares transactions</t>
         </is>
       </c>
+      <c r="I21">
+        <f>E21+F21+G21+H21</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>I21+J21</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>B21+C21+D21+K21</f>
+        <v/>
+      </c>
+      <c r="O21">
+        <f>L21+M21+N21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -591,6 +920,22 @@
           <t>Other transactions with owners</t>
         </is>
       </c>
+      <c r="I22">
+        <f>E22+F22+G22+H22</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>I22+J22</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>B22+C22+D22+K22</f>
+        <v/>
+      </c>
+      <c r="O22">
+        <f>L22+M22+N22</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -598,6 +943,22 @@
           <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
+      <c r="I23">
+        <f>E23+F23+G23+H23</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>I23+J23</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>B23+C23+D23+K23</f>
+        <v/>
+      </c>
+      <c r="O23">
+        <f>L23+M23+N23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -609,12 +970,80 @@
         <f>1*B13+1*B15+1*B16+-1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23</f>
         <v/>
       </c>
+      <c r="C24">
+        <f>1*C13+1*C15+1*C16+-1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>1*D13+1*D15+1*D16+-1*D17+1*D18+1*D19+1*D20+1*D21+1*D22+1*D23</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>1*E13+1*E15+1*E16+-1*E17+1*E18+1*E19+1*E20+1*E21+1*E22+1*E23</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>1*F13+1*F15+1*F16+-1*F17+1*F18+1*F19+1*F20+1*F21+1*F22+1*F23</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>1*G13+1*G15+1*G16+-1*G17+1*G18+1*G19+1*G20+1*G21+1*G22+1*G23</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>1*H13+1*H15+1*H16+-1*H17+1*H18+1*H19+1*H20+1*H21+1*H22+1*H23</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>E24+F24+G24+H24</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>1*J13+1*J15+1*J16+-1*J17+1*J18+1*J19+1*J20+1*J21+1*J22+1*J23</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>I24+J24</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>B24+C24+D24+K24</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>1*M13+1*M15+1*M16+-1*M17+1*M18+1*M19+1*M20+1*M21+1*M22+1*M23</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>1*N13+1*N15+1*N16+-1*N17+1*N18+1*N19+1*N20+1*N21+1*N22+1*N23</f>
+        <v/>
+      </c>
+      <c r="O24">
+        <f>L24+M24+N24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Equity at end of period</t>
         </is>
+      </c>
+      <c r="I25">
+        <f>E25+F25+G25+H25</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>I25+J25</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>B25+C25+D25+K25</f>
+        <v/>
+      </c>
+      <c r="O25">
+        <f>L25+M25+N25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -644,6 +1073,22 @@
           <t>Equity at beginning of period</t>
         </is>
       </c>
+      <c r="I30">
+        <f>E30+F30+G30+H30</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>I30+J30</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>B30+C30+D30+K30</f>
+        <v/>
+      </c>
+      <c r="O30">
+        <f>L30+M30+N30</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -651,6 +1096,22 @@
           <t>Impact of changes in accounting policies</t>
         </is>
       </c>
+      <c r="I31">
+        <f>E31+F31+G31+H31</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>I31+J31</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>B31+C31+D31+K31</f>
+        <v/>
+      </c>
+      <c r="O31">
+        <f>L31+M31+N31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -658,6 +1119,22 @@
           <t>Equity at beginning of period, restated</t>
         </is>
       </c>
+      <c r="I32">
+        <f>E32+F32+G32+H32</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>I32+J32</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>B32+C32+D32+K32</f>
+        <v/>
+      </c>
+      <c r="O32">
+        <f>L32+M32+N32</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -679,6 +1156,22 @@
           <t>Profit (loss)</t>
         </is>
       </c>
+      <c r="I35">
+        <f>E35+F35+G35+H35</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>I35+J35</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>B35+C35+D35+K35</f>
+        <v/>
+      </c>
+      <c r="O35">
+        <f>L35+M35+N35</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -686,6 +1179,22 @@
           <t>Total other comprehensive income</t>
         </is>
       </c>
+      <c r="I36">
+        <f>E36+F36+G36+H36</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>I36+J36</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>B36+C36+D36+K36</f>
+        <v/>
+      </c>
+      <c r="O36">
+        <f>L36+M36+N36</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -697,6 +1206,58 @@
         <f>1*B35+1*B36</f>
         <v/>
       </c>
+      <c r="C37">
+        <f>1*C35+1*C36</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>1*D35+1*D36</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>1*E35+1*E36</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>1*F35+1*F36</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>1*G35+1*G36</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>1*H35+1*H36</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>E37+F37+G37+H37</f>
+        <v/>
+      </c>
+      <c r="J37">
+        <f>1*J35+1*J36</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>I37+J37</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>B37+C37+D37+K37</f>
+        <v/>
+      </c>
+      <c r="M37">
+        <f>1*M35+1*M36</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>1*N35+1*N36</f>
+        <v/>
+      </c>
+      <c r="O37">
+        <f>L37+M37+N37</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -711,6 +1272,22 @@
           <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
+      <c r="I39">
+        <f>E39+F39+G39+H39</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>I39+J39</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>B39+C39+D39+K39</f>
+        <v/>
+      </c>
+      <c r="O39">
+        <f>L39+M39+N39</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -718,6 +1295,22 @@
           <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
+      <c r="I40">
+        <f>E40+F40+G40+H40</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>I40+J40</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>B40+C40+D40+K40</f>
+        <v/>
+      </c>
+      <c r="O40">
+        <f>L40+M40+N40</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -725,6 +1318,22 @@
           <t>Dividends paid</t>
         </is>
       </c>
+      <c r="I41">
+        <f>E41+F41+G41+H41</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>I41+J41</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>B41+C41+D41+K41</f>
+        <v/>
+      </c>
+      <c r="O41">
+        <f>L41+M41+N41</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -732,6 +1341,22 @@
           <t>Issuance of shares</t>
         </is>
       </c>
+      <c r="I42">
+        <f>E42+F42+G42+H42</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>I42+J42</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>B42+C42+D42+K42</f>
+        <v/>
+      </c>
+      <c r="O42">
+        <f>L42+M42+N42</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -739,6 +1364,22 @@
           <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
+      <c r="I43">
+        <f>E43+F43+G43+H43</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>I43+J43</f>
+        <v/>
+      </c>
+      <c r="L43">
+        <f>B43+C43+D43+K43</f>
+        <v/>
+      </c>
+      <c r="O43">
+        <f>L43+M43+N43</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -746,6 +1387,22 @@
           <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
+      <c r="I44">
+        <f>E44+F44+G44+H44</f>
+        <v/>
+      </c>
+      <c r="K44">
+        <f>I44+J44</f>
+        <v/>
+      </c>
+      <c r="L44">
+        <f>B44+C44+D44+K44</f>
+        <v/>
+      </c>
+      <c r="O44">
+        <f>L44+M44+N44</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -753,6 +1410,22 @@
           <t>Treasury shares transactions</t>
         </is>
       </c>
+      <c r="I45">
+        <f>E45+F45+G45+H45</f>
+        <v/>
+      </c>
+      <c r="K45">
+        <f>I45+J45</f>
+        <v/>
+      </c>
+      <c r="L45">
+        <f>B45+C45+D45+K45</f>
+        <v/>
+      </c>
+      <c r="O45">
+        <f>L45+M45+N45</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -760,6 +1433,22 @@
           <t>Other transactions with owners</t>
         </is>
       </c>
+      <c r="I46">
+        <f>E46+F46+G46+H46</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>I46+J46</f>
+        <v/>
+      </c>
+      <c r="L46">
+        <f>B46+C46+D46+K46</f>
+        <v/>
+      </c>
+      <c r="O46">
+        <f>L46+M46+N46</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -767,6 +1456,22 @@
           <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
+      <c r="I47">
+        <f>E47+F47+G47+H47</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>I47+J47</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>B47+C47+D47+K47</f>
+        <v/>
+      </c>
+      <c r="O47">
+        <f>L47+M47+N47</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -778,12 +1483,80 @@
         <f>1*B37+1*B39+1*B40+-1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47</f>
         <v/>
       </c>
+      <c r="C48">
+        <f>1*C37+1*C39+1*C40+-1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>1*D37+1*D39+1*D40+-1*D41+1*D42+1*D43+1*D44+1*D45+1*D46+1*D47</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>1*E37+1*E39+1*E40+-1*E41+1*E42+1*E43+1*E44+1*E45+1*E46+1*E47</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>1*F37+1*F39+1*F40+-1*F41+1*F42+1*F43+1*F44+1*F45+1*F46+1*F47</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>1*G37+1*G39+1*G40+-1*G41+1*G42+1*G43+1*G44+1*G45+1*G46+1*G47</f>
+        <v/>
+      </c>
+      <c r="H48">
+        <f>1*H37+1*H39+1*H40+-1*H41+1*H42+1*H43+1*H44+1*H45+1*H46+1*H47</f>
+        <v/>
+      </c>
+      <c r="I48">
+        <f>E48+F48+G48+H48</f>
+        <v/>
+      </c>
+      <c r="J48">
+        <f>1*J37+1*J39+1*J40+-1*J41+1*J42+1*J43+1*J44+1*J45+1*J46+1*J47</f>
+        <v/>
+      </c>
+      <c r="K48">
+        <f>I48+J48</f>
+        <v/>
+      </c>
+      <c r="L48">
+        <f>B48+C48+D48+K48</f>
+        <v/>
+      </c>
+      <c r="M48">
+        <f>1*M37+1*M39+1*M40+-1*M41+1*M42+1*M43+1*M44+1*M45+1*M46+1*M47</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>1*N37+1*N39+1*N40+-1*N41+1*N42+1*N43+1*N44+1*N45+1*N46+1*N47</f>
+        <v/>
+      </c>
+      <c r="O48">
+        <f>L48+M48+N48</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Equity at end of period</t>
         </is>
+      </c>
+      <c r="I49">
+        <f>E49+F49+G49+H49</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>I49+J49</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>B49+C49+D49+K49</f>
+        <v/>
+      </c>
+      <c r="O49">
+        <f>L49+M49+N49</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -813,6 +1586,22 @@
           <t>Equity at beginning of period</t>
         </is>
       </c>
+      <c r="I54">
+        <f>E54+F54+G54+H54</f>
+        <v/>
+      </c>
+      <c r="K54">
+        <f>I54+J54</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>B54+C54+D54+K54</f>
+        <v/>
+      </c>
+      <c r="O54">
+        <f>L54+M54+N54</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -820,6 +1609,22 @@
           <t>Impact of changes in accounting policies</t>
         </is>
       </c>
+      <c r="I55">
+        <f>E55+F55+G55+H55</f>
+        <v/>
+      </c>
+      <c r="K55">
+        <f>I55+J55</f>
+        <v/>
+      </c>
+      <c r="L55">
+        <f>B55+C55+D55+K55</f>
+        <v/>
+      </c>
+      <c r="O55">
+        <f>L55+M55+N55</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -827,6 +1632,22 @@
           <t>Equity at beginning of period, restated</t>
         </is>
       </c>
+      <c r="I56">
+        <f>E56+F56+G56+H56</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>I56+J56</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>B56+C56+D56+K56</f>
+        <v/>
+      </c>
+      <c r="O56">
+        <f>L56+M56+N56</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -848,6 +1669,22 @@
           <t>Profit (loss)</t>
         </is>
       </c>
+      <c r="I59">
+        <f>E59+F59+G59+H59</f>
+        <v/>
+      </c>
+      <c r="K59">
+        <f>I59+J59</f>
+        <v/>
+      </c>
+      <c r="L59">
+        <f>B59+C59+D59+K59</f>
+        <v/>
+      </c>
+      <c r="O59">
+        <f>L59+M59+N59</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -855,6 +1692,22 @@
           <t>Total other comprehensive income</t>
         </is>
       </c>
+      <c r="I60">
+        <f>E60+F60+G60+H60</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>I60+J60</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>B60+C60+D60+K60</f>
+        <v/>
+      </c>
+      <c r="O60">
+        <f>L60+M60+N60</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -866,6 +1719,58 @@
         <f>1*B59+1*B60</f>
         <v/>
       </c>
+      <c r="C61">
+        <f>1*C59+1*C60</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>1*D59+1*D60</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>1*E59+1*E60</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>1*F59+1*F60</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>1*G59+1*G60</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>1*H59+1*H60</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>E61+F61+G61+H61</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>1*J59+1*J60</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>I61+J61</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>B61+C61+D61+K61</f>
+        <v/>
+      </c>
+      <c r="M61">
+        <f>1*M59+1*M60</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>1*N59+1*N60</f>
+        <v/>
+      </c>
+      <c r="O61">
+        <f>L61+M61+N61</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -880,6 +1785,22 @@
           <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
+      <c r="I63">
+        <f>E63+F63+G63+H63</f>
+        <v/>
+      </c>
+      <c r="K63">
+        <f>I63+J63</f>
+        <v/>
+      </c>
+      <c r="L63">
+        <f>B63+C63+D63+K63</f>
+        <v/>
+      </c>
+      <c r="O63">
+        <f>L63+M63+N63</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -887,6 +1808,22 @@
           <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
+      <c r="I64">
+        <f>E64+F64+G64+H64</f>
+        <v/>
+      </c>
+      <c r="K64">
+        <f>I64+J64</f>
+        <v/>
+      </c>
+      <c r="L64">
+        <f>B64+C64+D64+K64</f>
+        <v/>
+      </c>
+      <c r="O64">
+        <f>L64+M64+N64</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -894,6 +1831,22 @@
           <t>Dividends paid</t>
         </is>
       </c>
+      <c r="I65">
+        <f>E65+F65+G65+H65</f>
+        <v/>
+      </c>
+      <c r="K65">
+        <f>I65+J65</f>
+        <v/>
+      </c>
+      <c r="L65">
+        <f>B65+C65+D65+K65</f>
+        <v/>
+      </c>
+      <c r="O65">
+        <f>L65+M65+N65</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -901,6 +1854,22 @@
           <t>Issuance of shares</t>
         </is>
       </c>
+      <c r="I66">
+        <f>E66+F66+G66+H66</f>
+        <v/>
+      </c>
+      <c r="K66">
+        <f>I66+J66</f>
+        <v/>
+      </c>
+      <c r="L66">
+        <f>B66+C66+D66+K66</f>
+        <v/>
+      </c>
+      <c r="O66">
+        <f>L66+M66+N66</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -908,6 +1877,22 @@
           <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
+      <c r="I67">
+        <f>E67+F67+G67+H67</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>I67+J67</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>B67+C67+D67+K67</f>
+        <v/>
+      </c>
+      <c r="O67">
+        <f>L67+M67+N67</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -915,6 +1900,22 @@
           <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
+      <c r="I68">
+        <f>E68+F68+G68+H68</f>
+        <v/>
+      </c>
+      <c r="K68">
+        <f>I68+J68</f>
+        <v/>
+      </c>
+      <c r="L68">
+        <f>B68+C68+D68+K68</f>
+        <v/>
+      </c>
+      <c r="O68">
+        <f>L68+M68+N68</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -922,6 +1923,22 @@
           <t>Treasury shares transactions</t>
         </is>
       </c>
+      <c r="I69">
+        <f>E69+F69+G69+H69</f>
+        <v/>
+      </c>
+      <c r="K69">
+        <f>I69+J69</f>
+        <v/>
+      </c>
+      <c r="L69">
+        <f>B69+C69+D69+K69</f>
+        <v/>
+      </c>
+      <c r="O69">
+        <f>L69+M69+N69</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -929,6 +1946,22 @@
           <t>Other transactions with owners</t>
         </is>
       </c>
+      <c r="I70">
+        <f>E70+F70+G70+H70</f>
+        <v/>
+      </c>
+      <c r="K70">
+        <f>I70+J70</f>
+        <v/>
+      </c>
+      <c r="L70">
+        <f>B70+C70+D70+K70</f>
+        <v/>
+      </c>
+      <c r="O70">
+        <f>L70+M70+N70</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -936,6 +1969,22 @@
           <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
+      <c r="I71">
+        <f>E71+F71+G71+H71</f>
+        <v/>
+      </c>
+      <c r="K71">
+        <f>I71+J71</f>
+        <v/>
+      </c>
+      <c r="L71">
+        <f>B71+C71+D71+K71</f>
+        <v/>
+      </c>
+      <c r="O71">
+        <f>L71+M71+N71</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -947,12 +1996,80 @@
         <f>1*B61+1*B63+1*B64+-1*B65+1*B66+1*B67+1*B68+1*B69+1*B70+1*B71</f>
         <v/>
       </c>
+      <c r="C72">
+        <f>1*C61+1*C63+1*C64+-1*C65+1*C66+1*C67+1*C68+1*C69+1*C70+1*C71</f>
+        <v/>
+      </c>
+      <c r="D72">
+        <f>1*D61+1*D63+1*D64+-1*D65+1*D66+1*D67+1*D68+1*D69+1*D70+1*D71</f>
+        <v/>
+      </c>
+      <c r="E72">
+        <f>1*E61+1*E63+1*E64+-1*E65+1*E66+1*E67+1*E68+1*E69+1*E70+1*E71</f>
+        <v/>
+      </c>
+      <c r="F72">
+        <f>1*F61+1*F63+1*F64+-1*F65+1*F66+1*F67+1*F68+1*F69+1*F70+1*F71</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>1*G61+1*G63+1*G64+-1*G65+1*G66+1*G67+1*G68+1*G69+1*G70+1*G71</f>
+        <v/>
+      </c>
+      <c r="H72">
+        <f>1*H61+1*H63+1*H64+-1*H65+1*H66+1*H67+1*H68+1*H69+1*H70+1*H71</f>
+        <v/>
+      </c>
+      <c r="I72">
+        <f>E72+F72+G72+H72</f>
+        <v/>
+      </c>
+      <c r="J72">
+        <f>1*J61+1*J63+1*J64+-1*J65+1*J66+1*J67+1*J68+1*J69+1*J70+1*J71</f>
+        <v/>
+      </c>
+      <c r="K72">
+        <f>I72+J72</f>
+        <v/>
+      </c>
+      <c r="L72">
+        <f>B72+C72+D72+K72</f>
+        <v/>
+      </c>
+      <c r="M72">
+        <f>1*M61+1*M63+1*M64+-1*M65+1*M66+1*M67+1*M68+1*M69+1*M70+1*M71</f>
+        <v/>
+      </c>
+      <c r="N72">
+        <f>1*N61+1*N63+1*N64+-1*N65+1*N66+1*N67+1*N68+1*N69+1*N70+1*N71</f>
+        <v/>
+      </c>
+      <c r="O72">
+        <f>L72+M72+N72</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Equity at end of period</t>
         </is>
+      </c>
+      <c r="I73">
+        <f>E73+F73+G73+H73</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>I73+J73</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>B73+C73+D73+K73</f>
+        <v/>
+      </c>
+      <c r="O73">
+        <f>L73+M73+N73</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -982,6 +2099,22 @@
           <t>Equity at beginning of period</t>
         </is>
       </c>
+      <c r="I78">
+        <f>E78+F78+G78+H78</f>
+        <v/>
+      </c>
+      <c r="K78">
+        <f>I78+J78</f>
+        <v/>
+      </c>
+      <c r="L78">
+        <f>B78+C78+D78+K78</f>
+        <v/>
+      </c>
+      <c r="O78">
+        <f>L78+M78+N78</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -989,6 +2122,22 @@
           <t>Impact of changes in accounting policies</t>
         </is>
       </c>
+      <c r="I79">
+        <f>E79+F79+G79+H79</f>
+        <v/>
+      </c>
+      <c r="K79">
+        <f>I79+J79</f>
+        <v/>
+      </c>
+      <c r="L79">
+        <f>B79+C79+D79+K79</f>
+        <v/>
+      </c>
+      <c r="O79">
+        <f>L79+M79+N79</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -996,6 +2145,22 @@
           <t>Equity at beginning of period, restated</t>
         </is>
       </c>
+      <c r="I80">
+        <f>E80+F80+G80+H80</f>
+        <v/>
+      </c>
+      <c r="K80">
+        <f>I80+J80</f>
+        <v/>
+      </c>
+      <c r="L80">
+        <f>B80+C80+D80+K80</f>
+        <v/>
+      </c>
+      <c r="O80">
+        <f>L80+M80+N80</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -1017,6 +2182,22 @@
           <t>Profit (loss)</t>
         </is>
       </c>
+      <c r="I83">
+        <f>E83+F83+G83+H83</f>
+        <v/>
+      </c>
+      <c r="K83">
+        <f>I83+J83</f>
+        <v/>
+      </c>
+      <c r="L83">
+        <f>B83+C83+D83+K83</f>
+        <v/>
+      </c>
+      <c r="O83">
+        <f>L83+M83+N83</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1024,6 +2205,22 @@
           <t>Total other comprehensive income</t>
         </is>
       </c>
+      <c r="I84">
+        <f>E84+F84+G84+H84</f>
+        <v/>
+      </c>
+      <c r="K84">
+        <f>I84+J84</f>
+        <v/>
+      </c>
+      <c r="L84">
+        <f>B84+C84+D84+K84</f>
+        <v/>
+      </c>
+      <c r="O84">
+        <f>L84+M84+N84</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1035,6 +2232,58 @@
         <f>1*B83+1*B84</f>
         <v/>
       </c>
+      <c r="C85">
+        <f>1*C83+1*C84</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>1*D83+1*D84</f>
+        <v/>
+      </c>
+      <c r="E85">
+        <f>1*E83+1*E84</f>
+        <v/>
+      </c>
+      <c r="F85">
+        <f>1*F83+1*F84</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>1*G83+1*G84</f>
+        <v/>
+      </c>
+      <c r="H85">
+        <f>1*H83+1*H84</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>E85+F85+G85+H85</f>
+        <v/>
+      </c>
+      <c r="J85">
+        <f>1*J83+1*J84</f>
+        <v/>
+      </c>
+      <c r="K85">
+        <f>I85+J85</f>
+        <v/>
+      </c>
+      <c r="L85">
+        <f>B85+C85+D85+K85</f>
+        <v/>
+      </c>
+      <c r="M85">
+        <f>1*M83+1*M84</f>
+        <v/>
+      </c>
+      <c r="N85">
+        <f>1*N83+1*N84</f>
+        <v/>
+      </c>
+      <c r="O85">
+        <f>L85+M85+N85</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1049,6 +2298,22 @@
           <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
+      <c r="I87">
+        <f>E87+F87+G87+H87</f>
+        <v/>
+      </c>
+      <c r="K87">
+        <f>I87+J87</f>
+        <v/>
+      </c>
+      <c r="L87">
+        <f>B87+C87+D87+K87</f>
+        <v/>
+      </c>
+      <c r="O87">
+        <f>L87+M87+N87</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1056,6 +2321,22 @@
           <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
+      <c r="I88">
+        <f>E88+F88+G88+H88</f>
+        <v/>
+      </c>
+      <c r="K88">
+        <f>I88+J88</f>
+        <v/>
+      </c>
+      <c r="L88">
+        <f>B88+C88+D88+K88</f>
+        <v/>
+      </c>
+      <c r="O88">
+        <f>L88+M88+N88</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1063,6 +2344,22 @@
           <t>Dividends paid</t>
         </is>
       </c>
+      <c r="I89">
+        <f>E89+F89+G89+H89</f>
+        <v/>
+      </c>
+      <c r="K89">
+        <f>I89+J89</f>
+        <v/>
+      </c>
+      <c r="L89">
+        <f>B89+C89+D89+K89</f>
+        <v/>
+      </c>
+      <c r="O89">
+        <f>L89+M89+N89</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1070,6 +2367,22 @@
           <t>Issuance of shares</t>
         </is>
       </c>
+      <c r="I90">
+        <f>E90+F90+G90+H90</f>
+        <v/>
+      </c>
+      <c r="K90">
+        <f>I90+J90</f>
+        <v/>
+      </c>
+      <c r="L90">
+        <f>B90+C90+D90+K90</f>
+        <v/>
+      </c>
+      <c r="O90">
+        <f>L90+M90+N90</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1077,6 +2390,22 @@
           <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
+      <c r="I91">
+        <f>E91+F91+G91+H91</f>
+        <v/>
+      </c>
+      <c r="K91">
+        <f>I91+J91</f>
+        <v/>
+      </c>
+      <c r="L91">
+        <f>B91+C91+D91+K91</f>
+        <v/>
+      </c>
+      <c r="O91">
+        <f>L91+M91+N91</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1084,6 +2413,22 @@
           <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
+      <c r="I92">
+        <f>E92+F92+G92+H92</f>
+        <v/>
+      </c>
+      <c r="K92">
+        <f>I92+J92</f>
+        <v/>
+      </c>
+      <c r="L92">
+        <f>B92+C92+D92+K92</f>
+        <v/>
+      </c>
+      <c r="O92">
+        <f>L92+M92+N92</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1091,6 +2436,22 @@
           <t>Treasury shares transactions</t>
         </is>
       </c>
+      <c r="I93">
+        <f>E93+F93+G93+H93</f>
+        <v/>
+      </c>
+      <c r="K93">
+        <f>I93+J93</f>
+        <v/>
+      </c>
+      <c r="L93">
+        <f>B93+C93+D93+K93</f>
+        <v/>
+      </c>
+      <c r="O93">
+        <f>L93+M93+N93</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1098,6 +2459,22 @@
           <t>Other transactions with owners</t>
         </is>
       </c>
+      <c r="I94">
+        <f>E94+F94+G94+H94</f>
+        <v/>
+      </c>
+      <c r="K94">
+        <f>I94+J94</f>
+        <v/>
+      </c>
+      <c r="L94">
+        <f>B94+C94+D94+K94</f>
+        <v/>
+      </c>
+      <c r="O94">
+        <f>L94+M94+N94</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1105,6 +2482,22 @@
           <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
+      <c r="I95">
+        <f>E95+F95+G95+H95</f>
+        <v/>
+      </c>
+      <c r="K95">
+        <f>I95+J95</f>
+        <v/>
+      </c>
+      <c r="L95">
+        <f>B95+C95+D95+K95</f>
+        <v/>
+      </c>
+      <c r="O95">
+        <f>L95+M95+N95</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1116,12 +2509,80 @@
         <f>1*B85+1*B87+1*B88+-1*B89+1*B90+1*B91+1*B92+1*B93+1*B94+1*B95</f>
         <v/>
       </c>
+      <c r="C96">
+        <f>1*C85+1*C87+1*C88+-1*C89+1*C90+1*C91+1*C92+1*C93+1*C94+1*C95</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>1*D85+1*D87+1*D88+-1*D89+1*D90+1*D91+1*D92+1*D93+1*D94+1*D95</f>
+        <v/>
+      </c>
+      <c r="E96">
+        <f>1*E85+1*E87+1*E88+-1*E89+1*E90+1*E91+1*E92+1*E93+1*E94+1*E95</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>1*F85+1*F87+1*F88+-1*F89+1*F90+1*F91+1*F92+1*F93+1*F94+1*F95</f>
+        <v/>
+      </c>
+      <c r="G96">
+        <f>1*G85+1*G87+1*G88+-1*G89+1*G90+1*G91+1*G92+1*G93+1*G94+1*G95</f>
+        <v/>
+      </c>
+      <c r="H96">
+        <f>1*H85+1*H87+1*H88+-1*H89+1*H90+1*H91+1*H92+1*H93+1*H94+1*H95</f>
+        <v/>
+      </c>
+      <c r="I96">
+        <f>E96+F96+G96+H96</f>
+        <v/>
+      </c>
+      <c r="J96">
+        <f>1*J85+1*J87+1*J88+-1*J89+1*J90+1*J91+1*J92+1*J93+1*J94+1*J95</f>
+        <v/>
+      </c>
+      <c r="K96">
+        <f>I96+J96</f>
+        <v/>
+      </c>
+      <c r="L96">
+        <f>B96+C96+D96+K96</f>
+        <v/>
+      </c>
+      <c r="M96">
+        <f>1*M85+1*M87+1*M88+-1*M89+1*M90+1*M91+1*M92+1*M93+1*M94+1*M95</f>
+        <v/>
+      </c>
+      <c r="N96">
+        <f>1*N85+1*N87+1*N88+-1*N89+1*N90+1*N91+1*N92+1*N93+1*N94+1*N95</f>
+        <v/>
+      </c>
+      <c r="O96">
+        <f>L96+M96+N96</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Equity at end of period</t>
         </is>
+      </c>
+      <c r="I97">
+        <f>E97+F97+G97+H97</f>
+        <v/>
+      </c>
+      <c r="K97">
+        <f>I97+J97</f>
+        <v/>
+      </c>
+      <c r="L97">
+        <f>B97+C97+D97+K97</f>
+        <v/>
+      </c>
+      <c r="O97">
+        <f>L97+M97+N97</f>
+        <v/>
       </c>
     </row>
   </sheetData>
